--- a/Data_Fig_03_O.xlsx
+++ b/Data_Fig_03_O.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Speed_m_s</t>
+          <t>Speed_BL_s</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
